--- a/Assets/CSV/Unit.xlsx
+++ b/Assets/CSV/Unit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Project_C\Assets\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33AFD86-E2C3-4F3E-9E1E-0C5BC43C3734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF99BF79-EA5B-4501-88C6-2B55D5EEF0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4935" yWindow="4935" windowWidth="28800" windowHeight="15345" xr2:uid="{D4F95642-F667-4BB1-8A94-2F4CA4F2C496}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -90,10 +90,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>o 현재 필드위에 공격력 버프</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>WolfKing</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -102,10 +98,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>o 다른필드위에 WolfBaby소환</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Fox</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -122,19 +114,23 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>o 다른필드의 저코스트 모두 흡수</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>디버프 상대 라인 공격력 저하</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Rabbit</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>o 랜덤 몬스터 다른라인으로 이동</t>
+    <t>상대의 랜덤 몬스터 다른라인으로 이동</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ability</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>다른필드위에 WolfBaby소환</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>다른필드의 저코스트 모두 흡수</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1118,16 +1114,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D19C08-AEAF-4ACF-8AEE-CB1287A86C70}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.75" customWidth="1"/>
+    <col min="7" max="7" width="40.875" customWidth="1"/>
+    <col min="8" max="8" width="36.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1144,19 +1141,22 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1172,20 +1172,23 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A2,".png")</f>
-        <v>Assets/Images/Monster.png</v>
-      </c>
-      <c r="G2">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A2,".png")</f>
+        <v>Assets/Images/Unit/Monster.png</v>
+      </c>
+      <c r="I2">
         <f>C2/D2</f>
         <v>1</v>
       </c>
-      <c r="H2">
-        <f>G2/B2</f>
+      <c r="J2">
+        <f>I2/B2</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1201,20 +1204,23 @@
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A3,".png")</f>
-        <v>Assets/Images/Monster1.png</v>
-      </c>
-      <c r="G3">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A3,".png")</f>
+        <v>Assets/Images/Unit/Monster1.png</v>
+      </c>
+      <c r="I3">
         <f>C3/D3</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H3">
-        <f>G3/B3</f>
+      <c r="J3">
+        <f>I3/B3</f>
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1230,23 +1236,23 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A4,".png")</f>
-        <v>Assets/Images/Squirrel.png</v>
-      </c>
-      <c r="G4">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A4,".png")</f>
+        <v>Assets/Images/Unit/Squirrel.png</v>
+      </c>
+      <c r="I4">
         <f>C4/D4</f>
         <v>1</v>
       </c>
-      <c r="H4">
-        <f>G4/B4</f>
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
+      <c r="J4">
+        <f>I4/B4</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1262,25 +1268,25 @@
       <c r="E5">
         <v>0.5</v>
       </c>
-      <c r="F5" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A5,".png")</f>
-        <v>Assets/Images/Hog.png</v>
-      </c>
-      <c r="G5">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A5,".png")</f>
+        <v>Assets/Images/Unit/Hog.png</v>
+      </c>
+      <c r="I5">
         <f>C5/D5</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="H5">
-        <f>G5/B5</f>
+      <c r="J5">
+        <f>I5/B5</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1294,23 +1300,23 @@
       <c r="E6">
         <v>1.5</v>
       </c>
-      <c r="F6" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A6,".png")</f>
-        <v>Assets/Images/WolfBaby.png</v>
-      </c>
-      <c r="G6">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A6,".png")</f>
+        <v>Assets/Images/Unit/WolfBaby.png</v>
+      </c>
+      <c r="I6">
         <f>C6/D6</f>
         <v>2</v>
       </c>
-      <c r="H6">
-        <f>G6/B6</f>
-        <v>2</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
+      <c r="J6">
+        <f>I6/B6</f>
+        <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1326,25 +1332,25 @@
       <c r="E7">
         <v>1.2</v>
       </c>
-      <c r="F7" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A7,".png")</f>
-        <v>Assets/Images/Raccoon.png</v>
-      </c>
-      <c r="G7">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A7,".png")</f>
+        <v>Assets/Images/Unit/Raccoon.png</v>
+      </c>
+      <c r="I7">
         <f>C7/D7</f>
         <v>4</v>
       </c>
-      <c r="H7">
-        <f>G7/B7</f>
-        <v>2</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
+      <c r="J7">
+        <f>I7/B7</f>
+        <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -1358,23 +1364,26 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A8,".png")</f>
-        <v>Assets/Images/Rabbit.png</v>
-      </c>
-      <c r="G8">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A8,".png")</f>
+        <v>Assets/Images/Unit/Rabbit.png</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8">
         <f>C8/D8</f>
         <v>2</v>
       </c>
-      <c r="H8">
-        <f>G8/B8</f>
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>28</v>
+      <c r="J8">
+        <f>I8/B8</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1390,25 +1399,29 @@
       <c r="E9">
         <v>2</v>
       </c>
-      <c r="F9" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A9,".png")</f>
-        <v>Assets/Images/Cat.png</v>
-      </c>
-      <c r="G9">
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A9,".png")</f>
+        <v>Assets/Images/Unit/Cat.png</v>
+      </c>
+      <c r="H9" t="str">
+        <f>_xlfn.CONCAT("현재 필드위에 공격력 버프 +",F9)</f>
+        <v>현재 필드위에 공격력 버프 +2</v>
+      </c>
+      <c r="I9">
         <f>C9/D9</f>
         <v>6</v>
       </c>
-      <c r="H9">
-        <f>G9/B9</f>
-        <v>2</v>
-      </c>
-      <c r="I9" t="s">
-        <v>17</v>
+      <c r="J9">
+        <f>I9/B9</f>
+        <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -1422,22 +1435,25 @@
       <c r="E10">
         <v>1.5</v>
       </c>
-      <c r="F10" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A10,".png")</f>
-        <v>Assets/Images/Fox.png</v>
-      </c>
-      <c r="G10">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A10,".png")</f>
+        <v>Assets/Images/Unit/Fox.png</v>
+      </c>
+      <c r="I10">
         <f>C10/D10</f>
         <v>7</v>
       </c>
-      <c r="H10">
-        <f>G10/B10</f>
+      <c r="J10">
+        <f>I10/B10</f>
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -1451,23 +1467,27 @@
       <c r="E11">
         <v>1.5</v>
       </c>
-      <c r="F11" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A11,".png")</f>
-        <v>Assets/Images/Snake.png</v>
-      </c>
-      <c r="G11">
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A11,".png")</f>
+        <v>Assets/Images/Unit/Snake.png</v>
+      </c>
+      <c r="H11" t="str">
+        <f>_xlfn.CONCAT("디버프 상대 라인 공격력 저하 -",F11)</f>
+        <v>디버프 상대 라인 공격력 저하 -2</v>
+      </c>
+      <c r="I11">
         <f>C11/D11</f>
         <v>3</v>
       </c>
-      <c r="H11">
-        <f>G11/B11</f>
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>26</v>
+      <c r="J11">
+        <f>I11/B11</f>
+        <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1483,25 +1503,28 @@
       <c r="E12">
         <v>1.5</v>
       </c>
-      <c r="F12" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A12,".png")</f>
-        <v>Assets/Images/Bear.png</v>
-      </c>
-      <c r="G12">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A12,".png")</f>
+        <v>Assets/Images/Unit/Bear.png</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12">
         <f>C12/D12</f>
         <v>9</v>
       </c>
-      <c r="H12">
-        <f>G12/B12</f>
+      <c r="J12">
+        <f>I12/B12</f>
         <v>2.25</v>
       </c>
-      <c r="I12" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -1515,25 +1538,28 @@
       <c r="E13">
         <v>2</v>
       </c>
-      <c r="F13" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A13,".png")</f>
-        <v>Assets/Images/WolfKing.png</v>
-      </c>
-      <c r="G13">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A13,".png")</f>
+        <v>Assets/Images/Unit/WolfKing.png</v>
+      </c>
+      <c r="H13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13">
         <f>C13/D13</f>
         <v>9</v>
       </c>
-      <c r="H13">
-        <f>G13/B13</f>
+      <c r="J13">
+        <f>I13/B13</f>
         <v>2.25</v>
       </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -1547,22 +1573,25 @@
       <c r="E14">
         <v>2</v>
       </c>
-      <c r="F14" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A14,".png")</f>
-        <v>Assets/Images/Deer.png</v>
-      </c>
-      <c r="G14">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A14,".png")</f>
+        <v>Assets/Images/Unit/Deer.png</v>
+      </c>
+      <c r="I14">
         <f>C14/D14</f>
         <v>12</v>
       </c>
-      <c r="H14">
-        <f>G14/B14</f>
+      <c r="J14">
+        <f>I14/B14</f>
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>8</v>
@@ -1576,20 +1605,23 @@
       <c r="E15">
         <v>2</v>
       </c>
-      <c r="F15" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/",A15,".png")</f>
-        <v>Assets/Images/Tiger.png</v>
-      </c>
-      <c r="G15">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="str">
+        <f>_xlfn.CONCAT("Assets/Images/Unit/",A15,".png")</f>
+        <v>Assets/Images/Unit/Tiger.png</v>
+      </c>
+      <c r="H15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15">
         <f>C15/D15</f>
         <v>12.857142857142858</v>
       </c>
-      <c r="H15">
-        <f>G15/B15</f>
+      <c r="J15">
+        <f>I15/B15</f>
         <v>1.6071428571428572</v>
-      </c>
-      <c r="I15" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/CSV/Unit.xlsx
+++ b/Assets/CSV/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Project_C\Assets\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF99BF79-EA5B-4501-88C6-2B55D5EEF0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3AEE886-BBA0-4783-BDCA-4D1333C681AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4935" yWindow="4935" windowWidth="28800" windowHeight="15345" xr2:uid="{D4F95642-F667-4BB1-8A94-2F4CA4F2C496}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D4F95642-F667-4BB1-8A94-2F4CA4F2C496}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -65,9 +65,6 @@
     <t>Monster1</t>
   </si>
   <si>
-    <t>Squirrel</t>
-  </si>
-  <si>
     <t>Hog</t>
   </si>
   <si>
@@ -131,6 +128,10 @@
   </si>
   <si>
     <t>다른필드의 저코스트 모두 흡수</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mouse</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1141,13 +1142,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
@@ -1176,15 +1177,15 @@
         <v>0</v>
       </c>
       <c r="G2" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A2,".png")</f>
+        <f t="shared" ref="G2:G15" si="0">_xlfn.CONCAT("Assets/Images/Unit/",A2,".png")</f>
         <v>Assets/Images/Unit/Monster.png</v>
       </c>
       <c r="I2">
-        <f>C2/D2</f>
+        <f t="shared" ref="I2:I15" si="1">C2/D2</f>
         <v>1</v>
       </c>
       <c r="J2">
-        <f>I2/B2</f>
+        <f t="shared" ref="J2:J15" si="2">I2/B2</f>
         <v>1</v>
       </c>
     </row>
@@ -1208,21 +1209,21 @@
         <v>0</v>
       </c>
       <c r="G3" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A3,".png")</f>
+        <f t="shared" si="0"/>
         <v>Assets/Images/Unit/Monster1.png</v>
       </c>
       <c r="I3">
-        <f>C3/D3</f>
+        <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="J3">
-        <f>I3/B3</f>
+        <f t="shared" si="2"/>
         <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1240,21 +1241,21 @@
         <v>0</v>
       </c>
       <c r="G4" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A4,".png")</f>
-        <v>Assets/Images/Unit/Squirrel.png</v>
+        <f t="shared" si="0"/>
+        <v>Assets/Images/Unit/Mouse.png</v>
       </c>
       <c r="I4">
-        <f>C4/D4</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J4">
-        <f>I4/B4</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1272,21 +1273,21 @@
         <v>0</v>
       </c>
       <c r="G5" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A5,".png")</f>
+        <f t="shared" si="0"/>
         <v>Assets/Images/Unit/Hog.png</v>
       </c>
       <c r="I5">
-        <f>C5/D5</f>
+        <f t="shared" si="1"/>
         <v>1.3333333333333333</v>
       </c>
       <c r="J5">
-        <f>I5/B5</f>
+        <f t="shared" si="2"/>
         <v>1.3333333333333333</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1304,21 +1305,21 @@
         <v>0</v>
       </c>
       <c r="G6" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A6,".png")</f>
+        <f t="shared" si="0"/>
         <v>Assets/Images/Unit/WolfBaby.png</v>
       </c>
       <c r="I6">
-        <f>C6/D6</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J6">
-        <f>I6/B6</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -1336,56 +1337,56 @@
         <v>0</v>
       </c>
       <c r="G7" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A7,".png")</f>
+        <f t="shared" si="0"/>
         <v>Assets/Images/Unit/Raccoon.png</v>
       </c>
       <c r="I7">
-        <f>C7/D7</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="J7">
-        <f>I7/B7</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Images/Unit/Rabbit.png</v>
+      </c>
+      <c r="H8" t="s">
         <v>23</v>
       </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A8,".png")</f>
-        <v>Assets/Images/Unit/Rabbit.png</v>
-      </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
       <c r="I8">
-        <f>C8/D8</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J8">
-        <f>I8/B8</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -1403,7 +1404,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A9,".png")</f>
+        <f t="shared" si="0"/>
         <v>Assets/Images/Unit/Cat.png</v>
       </c>
       <c r="H9" t="str">
@@ -1411,17 +1412,17 @@
         <v>현재 필드위에 공격력 버프 +2</v>
       </c>
       <c r="I9">
-        <f>C9/D9</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="J9">
-        <f>I9/B9</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -1439,21 +1440,21 @@
         <v>0</v>
       </c>
       <c r="G10" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A10,".png")</f>
+        <f t="shared" si="0"/>
         <v>Assets/Images/Unit/Fox.png</v>
       </c>
       <c r="I10">
-        <f>C10/D10</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="J10">
-        <f>I10/B10</f>
+        <f t="shared" si="2"/>
         <v>2.3333333333333335</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -1471,7 +1472,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A11,".png")</f>
+        <f t="shared" si="0"/>
         <v>Assets/Images/Unit/Snake.png</v>
       </c>
       <c r="H11" t="str">
@@ -1479,17 +1480,17 @@
         <v>디버프 상대 라인 공격력 저하 -2</v>
       </c>
       <c r="I11">
-        <f>C11/D11</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="J11">
-        <f>I11/B11</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>4</v>
@@ -1507,24 +1508,24 @@
         <v>0</v>
       </c>
       <c r="G12" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A12,".png")</f>
+        <f t="shared" si="0"/>
         <v>Assets/Images/Unit/Bear.png</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I12">
-        <f>C12/D12</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="J12">
-        <f>I12/B12</f>
+        <f t="shared" si="2"/>
         <v>2.25</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -1542,24 +1543,24 @@
         <v>0</v>
       </c>
       <c r="G13" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A13,".png")</f>
+        <f t="shared" si="0"/>
         <v>Assets/Images/Unit/WolfKing.png</v>
       </c>
       <c r="H13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I13">
-        <f>C13/D13</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="J13">
-        <f>I13/B13</f>
+        <f t="shared" si="2"/>
         <v>2.25</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -1577,21 +1578,21 @@
         <v>0</v>
       </c>
       <c r="G14" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A14,".png")</f>
+        <f t="shared" si="0"/>
         <v>Assets/Images/Unit/Deer.png</v>
       </c>
       <c r="I14">
-        <f>C14/D14</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="J14">
-        <f>I14/B14</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>8</v>
@@ -1609,18 +1610,18 @@
         <v>0</v>
       </c>
       <c r="G15" t="str">
-        <f>_xlfn.CONCAT("Assets/Images/Unit/",A15,".png")</f>
+        <f t="shared" si="0"/>
         <v>Assets/Images/Unit/Tiger.png</v>
       </c>
       <c r="H15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I15">
-        <f>C15/D15</f>
+        <f t="shared" si="1"/>
         <v>12.857142857142858</v>
       </c>
       <c r="J15">
-        <f>I15/B15</f>
+        <f t="shared" si="2"/>
         <v>1.6071428571428572</v>
       </c>
     </row>
